--- a/out/MLP-mamba2_repeat_5_000006.xlsx
+++ b/out/MLP-mamba2_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.503542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.386750013692762</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.503542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.503542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.103542575915647</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.503542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7867500136927614</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.503542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.503542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.386750013692762</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7867500136927614</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7867500136927614</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.386750013692762</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003414639360823203</v>
+        <v>-0.0003312591825251002</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4394904740363528</v>
+        <v>0.4263563717582778</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7867500136927614</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8798130973412301</v>
+        <v>0.8535196148612464</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1014965121418847</v>
+        <v>-0.09846321086311462</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3376524979583856</v>
+        <v>0.3275619017126381</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.503542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3376524979583856</v>
+        <v>0.3275619017126381</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.103542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3372816047668282</v>
+        <v>0.3272708787712294</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.139463935014149</v>
+        <v>0.8940854153413883</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.618478738998788</v>
+        <v>2.117222042488683</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2180236469767364</v>
+        <v>0.171073169980784</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.103542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.91339894831006</v>
+        <v>1.563978224420733</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3818890946258914</v>
+        <v>0.2996506639372788</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.503542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.459260364100212</v>
+        <v>1.992290676546317</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2091363653887807</v>
+        <v>0.1640996080382148</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7867500136927614</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.495314834926718</v>
+        <v>2.020580989431484</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08637616780721427</v>
+        <v>0.06777552794953214</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.458711959047085</v>
+        <v>1.991860326724106</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1076177832045682</v>
+        <v>0.08444249172117829</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.587585461945422</v>
+        <v>2.092981746135476</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0647998067328663</v>
+        <v>0.05084528765262418</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.103542575915647</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.609494262867648</v>
+        <v>2.110172727760055</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04926527313577481</v>
+        <v>0.03865608726581413</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.103542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.643197312656199</v>
+        <v>2.136618503600552</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02179015851687477</v>
+        <v>0.01709848238852397</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.103542575915647</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.637468905498106</v>
+        <v>2.13212348954037</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01728939416196004</v>
+        <v>0.01356702176711843</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.103542575915647</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.650252211070228</v>
+        <v>2.142153645509855</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008572575822873007</v>
+        <v>0.006723981908290576</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.103542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.650094122630363</v>
+        <v>2.142028529126906</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004981370078009033</v>
+        <v>0.003907875002871733</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.103542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.651482667500785</v>
+        <v>2.143117151344136</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002488185039004517</v>
+        <v>0.001952892101808681</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.651474563317108</v>
+        <v>2.143109713636301</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.00122822406166175</v>
+        <v>0.000960881782560252</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.651438345488727</v>
+        <v>2.143080228715081</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007092576944711856</v>
+        <v>0.0005557256666876598</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.651631327810877</v>
+        <v>2.143230753733409</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002338208021949941</v>
+        <v>0.0001824854895736403</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.65138801991997</v>
+        <v>2.143038432947512</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001162727219526363</v>
+        <v>8.932322818538381e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.651384361829343</v>
+        <v>2.143034490492441</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.104729551292968e-05</v>
+        <v>4.637011873227863e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.651390113921549</v>
+        <v>2.143038053876581</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>2.107198491659588e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.503542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.651383020363089</v>
+        <v>2.143031346802279</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7867500136927614</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.651385550358631</v>
+        <v>2.143032265038423</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.651378215964488</v>
+        <v>2.143025262747603</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.65137473074418</v>
+        <v>2.143021400672506</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.651370183431994</v>
+        <v>2.143016853360321</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.651370273376644</v>
+        <v>2.143016943304971</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.651369415443059</v>
+        <v>2.143016085371386</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.651369643764094</v>
+        <v>2.143016313692421</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.651368848099883</v>
+        <v>2.143015518028209</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.651368910369256</v>
+        <v>2.143015580297582</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.651368938044533</v>
+        <v>2.143015607972859</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.386750013692762</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.651369090258556</v>
+        <v>2.143015760186882</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.651368744317594</v>
+        <v>2.143015414245921</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.651368820424606</v>
+        <v>2.143015490352932</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.651368986476267</v>
+        <v>2.143015656404594</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.651369346254867</v>
+        <v>2.143016016183194</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.651369367011325</v>
+        <v>2.143016036939652</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.651369470793613</v>
+        <v>2.14301614072194</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.651369699114648</v>
+        <v>2.143016369042975</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.651369574575902</v>
+        <v>2.143016244504229</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.651369602251179</v>
+        <v>2.143016272179506</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.503542575915647</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.651369657601733</v>
+        <v>2.143016327530059</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.651369920516863</v>
+        <v>2.14301659044519</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.651369837491033</v>
+        <v>2.143016507419359</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.651369629926456</v>
+        <v>2.143016299854783</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.651369643764094</v>
+        <v>2.143016313692421</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.651369782140479</v>
+        <v>2.143016452068806</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.65136949846889</v>
+        <v>2.143016168397217</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.651369325498409</v>
+        <v>2.143015995426736</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.651369221716121</v>
+        <v>2.143015891644448</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.651369367011325</v>
+        <v>2.143016036939652</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.651369609169998</v>
+        <v>2.143016279098325</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.651369436199517</v>
+        <v>2.143016106127844</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.651369138690291</v>
+        <v>2.143015808618617</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.651369124852652</v>
+        <v>2.143015794780978</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.651368758155232</v>
+        <v>2.143015428083559</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.651368758155232</v>
+        <v>2.143015428083559</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.651368695885859</v>
+        <v>2.143015365814186</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.651368592103571</v>
+        <v>2.143015262031898</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.65136841913309</v>
+        <v>2.143015089061417</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.651368467564824</v>
+        <v>2.143015137493151</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.651368107786225</v>
+        <v>2.143014777714551</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.103542575915647</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.651368066273309</v>
+        <v>2.143014736201636</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.651368121623863</v>
+        <v>2.14301479155219</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.651368176974417</v>
+        <v>2.143014846902744</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.651368218487332</v>
+        <v>2.143014888415659</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.651367948653382</v>
+        <v>2.143014618581709</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.651368004003936</v>
+        <v>2.143014673932263</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.65136814929914</v>
+        <v>2.143014819227467</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.651368114705044</v>
+        <v>2.143014784633371</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.651368100867406</v>
+        <v>2.143014770795732</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.651368190812056</v>
+        <v>2.143014860740382</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.65136850907774</v>
+        <v>2.143015179006067</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.65136832918844</v>
+        <v>2.143014999116767</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.651368370701356</v>
+        <v>2.143015040629682</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.651368183893236</v>
+        <v>2.143014853821563</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.651368253081428</v>
+        <v>2.143014923009755</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.651368052435671</v>
+        <v>2.143014722363998</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.651368093948586</v>
+        <v>2.143014763876913</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.103542575915647</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.651368121623863</v>
+        <v>2.14301479155219</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_5_000006.xlsx
+++ b/out/MLP-mamba2_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.503542575915647</v>
+        <v>0.2057574499049892</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003414639360823203</v>
+        <v>-0.0001844936767758336</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4394904740363528</v>
+        <v>0.2374577333762636</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8798130973412301</v>
+        <v>0.4753648510078776</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1014965121418847</v>
+        <v>-0.05483875091647519</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3376524979583856</v>
+        <v>0.1824344887830126</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.503542575915647</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3376524979583856</v>
+        <v>0.1824344887830126</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3372816047668282</v>
+        <v>0.182242897336574</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.139463935014149</v>
+        <v>0.5886101965423082</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.618478738998788</v>
+        <v>1.360635676081652</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2180236469767364</v>
+        <v>0.1126239909492847</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.91339894831006</v>
+        <v>0.9964141750372077</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3818890946258914</v>
+        <v>0.1972713836551376</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.503542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.459260364100212</v>
+        <v>1.278388594291932</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2091363653887807</v>
+        <v>0.1080332267747053</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.495314834926718</v>
+        <v>1.29701319272464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08637616780721427</v>
+        <v>0.04461909916553927</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.458711959047085</v>
+        <v>1.278105305780896</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1076177832045682</v>
+        <v>0.05559205902723764</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.587585461945422</v>
+        <v>1.344677420229237</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0647998067328663</v>
+        <v>0.03347360049221104</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.609494262867648</v>
+        <v>1.355994837461008</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04926527313577481</v>
+        <v>0.02544803700549739</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.643197312656199</v>
+        <v>1.373404804765413</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02179015851687477</v>
+        <v>0.01125513428450758</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.637468905498106</v>
+        <v>1.370444187113562</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01728939416196004</v>
+        <v>0.008928674242544784</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.650252211070228</v>
+        <v>1.37704568191311</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008572575822873007</v>
+        <v>0.004425121546313238</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.650094122630363</v>
+        <v>1.376961594482111</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004981370078009033</v>
+        <v>0.002572551860627773</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.651482667500785</v>
+        <v>1.377676733969181</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002488185039004517</v>
+        <v>0.001283775930313887</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.651474563317108</v>
+        <v>1.377670129356148</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.00122822406166175</v>
+        <v>0.0006302972438863562</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.651438345488727</v>
+        <v>1.377649012850462</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007092576944711856</v>
+        <v>0.0003654794583472038</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.651631327810877</v>
+        <v>1.377746464170556</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002338208021949941</v>
+        <v>0.0001177583562684549</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.65138801991997</v>
+        <v>1.377618431473584</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001162727219526363</v>
+        <v>5.788215212358921e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.651384361829343</v>
+        <v>1.377614127278445</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.104729551292968e-05</v>
+        <v>2.924674582151908e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.651390113921549</v>
+        <v>1.377614702437366</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>1.159126312874283e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.651383020363089</v>
+        <v>1.377608616117356</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.651385550358631</v>
+        <v>1.377607382926203</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.651378215964488</v>
+        <v>1.377601048065656</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.65137473074418</v>
+        <v>1.377596805455502</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.651370183431994</v>
+        <v>1.377597033776537</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.651370273376644</v>
+        <v>1.377597123721187</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.651369415443059</v>
+        <v>1.377596265787602</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.651369643764094</v>
+        <v>1.377596494108637</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.651368848099883</v>
+        <v>1.377595698444425</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.651368910369256</v>
+        <v>1.377595760713798</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.651368938044533</v>
+        <v>1.377595788389075</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.651369090258556</v>
+        <v>1.377595940603098</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.651368744317594</v>
+        <v>1.377595594662136</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.651368820424606</v>
+        <v>1.377595670769148</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.651368986476267</v>
+        <v>1.37759583682081</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.651369346254867</v>
+        <v>1.377596196599409</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.651369367011325</v>
+        <v>1.377596217355867</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.651369470793613</v>
+        <v>1.377596321138156</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.651369699114648</v>
+        <v>1.377596549459191</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.651369574575902</v>
+        <v>1.377596424920444</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.651369602251179</v>
+        <v>1.377596452595721</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.651369657601733</v>
+        <v>1.377596507946275</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.651369920516863</v>
+        <v>1.377596770861406</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.651369837491033</v>
+        <v>1.377596687835575</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.651369629926456</v>
+        <v>1.377596480270998</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.651369643764094</v>
+        <v>1.377596494108637</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.651369782140479</v>
+        <v>1.377596632485021</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.65136949846889</v>
+        <v>1.377596348813433</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.651369325498409</v>
+        <v>1.377596175842952</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.651369221716121</v>
+        <v>1.377596072060664</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.651369367011325</v>
+        <v>1.377596217355867</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.651369609169998</v>
+        <v>1.377596459514541</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.651369436199517</v>
+        <v>1.37759628654406</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.651369138690291</v>
+        <v>1.377595989034833</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.651369124852652</v>
+        <v>1.377595975197194</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.651368758155232</v>
+        <v>1.377595608499775</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.651368758155232</v>
+        <v>1.377595608499775</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.651368695885859</v>
+        <v>1.377595546230402</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.651368592103571</v>
+        <v>1.377595442448113</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.65136841913309</v>
+        <v>1.377595269477632</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.651368467564824</v>
+        <v>1.377595317909367</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.651368107786225</v>
+        <v>1.377594958130767</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.651368066273309</v>
+        <v>1.377594916617852</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.651368121623863</v>
+        <v>1.377594971968406</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.651368176974417</v>
+        <v>1.37759502731896</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.651368218487332</v>
+        <v>1.377595068831875</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.651367948653382</v>
+        <v>1.377594798997925</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.651368004003936</v>
+        <v>1.377594854348478</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.65136814929914</v>
+        <v>1.377594999643682</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.651368114705044</v>
+        <v>1.377594965049586</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.651368100867406</v>
+        <v>1.377594951211948</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.651368190812056</v>
+        <v>1.377595041156598</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.65136850907774</v>
+        <v>1.377595359422282</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.65136832918844</v>
+        <v>1.377595179532982</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.651368370701356</v>
+        <v>1.377595221045898</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.651368183893236</v>
+        <v>1.377595034237779</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.651368253081428</v>
+        <v>1.377595103425971</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.651368052435671</v>
+        <v>1.377594902780213</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.651368093948586</v>
+        <v>1.377594944293129</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.103542575915647</v>
+        <v>0.2057574499049892</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.651368121623863</v>
+        <v>1.377594971968406</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_5_000006.xlsx
+++ b/out/MLP-mamba2_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.5078936219215393</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.2057574499049892</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.481170654296875</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.536076603003093</v>
+        <v>-0.09000000000000008</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5056397914886475</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.6547783017158508</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.1976152211427689</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.6162081360816956</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.32485231757164</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4807814955711365</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5317714810371399</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2110555320978165</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4559471011161804</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3860459327697754</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.651511013507843</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3148402869701385</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.306688517332077</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2963784039020538</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.5226413607597351</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.5331536531448364</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.396714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.6493722200393677</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3910776674747467</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2192174047231674</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.385403573513031</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3247998654842377</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.6990628838539124</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.2815493941307068</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.892791748046875</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5664863586425781</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.493395984172821</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3253392279148102</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5877752900123596</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1245617031931146</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3369349241256714</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3015113472938538</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4891141057014465</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.7103826999664307</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4116252958774567</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4129025638103485</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.669799268245697</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.351017951965332</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.447949081659317</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4946617186069489</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1245617031931146</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.7973765134811401</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8938533663749695</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.396714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.8373579382896423</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001844936767758336</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2374577333762636</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.281499058008194</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4753648510078776</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05483875091647519</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.03590704873204231</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1824344887830126</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.7025089859962463</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.536076603003093</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1824344887830126</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.7973305583000183</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.182242897336574</v>
+        <v>0.1487550174629798</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5886101965423082</v>
+        <v>0.2220724527183046</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.2384816706180573</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.360635676081652</v>
+        <v>0.5933421210574857</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1126239909492847</v>
+        <v>0.04249106159216588</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.8537209033966064</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9964141750372077</v>
+        <v>0.4559277202391059</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1972713836551376</v>
+        <v>0.07442712414977931</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.6238150596618652</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.278388594291932</v>
+        <v>0.5623117357381268</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1080332267747053</v>
+        <v>0.04075900163180279</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3621461093425751</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.29701319272464</v>
+        <v>0.5693384631679523</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04461909916553927</v>
+        <v>0.01683406125898829</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.8707981109619141</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.278105305780896</v>
+        <v>0.5622048559150095</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05559205902723764</v>
+        <v>0.0209733053068108</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.8623257875442505</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.344677420229237</v>
+        <v>0.5873212124477022</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03347360049221104</v>
+        <v>0.01262836336797664</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.832460343837738</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.396714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.355994837461008</v>
+        <v>0.5915902860940718</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02544803700549739</v>
+        <v>0.009599664042752726</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5764890313148499</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.373404804765413</v>
+        <v>0.5981569335121708</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01125513428450758</v>
+        <v>0.00424317769124753</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.68604576587677</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.370444187113562</v>
+        <v>0.5970368500988474</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.008928674242544784</v>
+        <v>0.003364674982507011</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.537279486656189</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.396714909199301</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.37704568191311</v>
+        <v>0.5995243225849434</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004425121546313238</v>
+        <v>0.001665988815887771</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9104500412940979</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.396714909199301</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.376961594482111</v>
+        <v>0.5994894788253274</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002572551860627773</v>
+        <v>0.0009666730490402668</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.6095370054244995</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.377676733969181</v>
+        <v>0.59975636174072</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001283775930313887</v>
+        <v>0.0004808365245201334</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.05703156068921089</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.377670129356148</v>
+        <v>0.5997507568414505</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006302972438863562</v>
+        <v>0.000236470445640063</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.1962161064147949</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.377649012850462</v>
+        <v>0.5997396442596696</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003654794583472038</v>
+        <v>0.0001351814166719149</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.1132867559790611</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.377746464170556</v>
+        <v>0.5997734096240291</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001177583562684549</v>
+        <v>4.187137239341006e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.1033474057912827</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.377618431473584</v>
+        <v>0.5997218561803243</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>5.788215212358921e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.2274884432554245</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.377614127278445</v>
+        <v>0.5997171185196988</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.924674582151908e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.1689743995666504</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.377614702437366</v>
+        <v>0.5997143102936427</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.7095217108726501</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.377608616117356</v>
+        <v>0.5997088447279239</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.2720710337162018</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.377607382926203</v>
+        <v>0.599705460109473</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4985755383968353</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.377601048065656</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.5323192477226257</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.377596805455502</v>
+        <v>0.5997001732142569</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.1241387575864792</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.377597033776537</v>
+        <v>0.5997004015352917</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.05662895739078522</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5852000093893223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.377597123721187</v>
+        <v>0.5997004914799416</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2337480038404465</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.377596265787602</v>
+        <v>0.5996996335463568</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.09818444401025772</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.377596494108637</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3137547969818115</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.377595698444425</v>
+        <v>0.5996990662031798</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.1858896166086197</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.377595760713798</v>
+        <v>0.5996991284725529</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3838466703891754</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.377595788389075</v>
+        <v>0.5996991561478298</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4551865756511688</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.377595940603098</v>
+        <v>0.599699308361853</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2276037633419037</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.377595594662136</v>
+        <v>0.5996989624208913</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5518461465835571</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.377595670769148</v>
+        <v>0.599699038527903</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2689307630062103</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.37759583682081</v>
+        <v>0.5996992045795645</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.779538631439209</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.377596196599409</v>
+        <v>0.5996995643581645</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5412673950195312</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.377596217355867</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.6429377198219299</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.377596321138156</v>
+        <v>0.5996996888969107</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.2135288417339325</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.377596549459191</v>
+        <v>0.5996999172179455</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.2159094661474228</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.377596424920444</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3427782654762268</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.377596452595721</v>
+        <v>0.5996998203544761</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.6667807102203369</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.377596507946275</v>
+        <v>0.59969987570503</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.147905707359314</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.377596770861406</v>
+        <v>0.5997001386201608</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2760295569896698</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.377596687835575</v>
+        <v>0.5997000555943299</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3919332325458527</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.377596480270998</v>
+        <v>0.5996998480297532</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4093905985355377</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.377596494108637</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2424729317426682</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.377596632485021</v>
+        <v>0.5997000002437762</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.1754699051380157</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.377596348813433</v>
+        <v>0.5996997165721876</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2487944066524506</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.377596175842952</v>
+        <v>0.5996995436017069</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6692742109298706</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.377596072060664</v>
+        <v>0.5996994398194183</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.5867109894752502</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.377596217355867</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3608028292655945</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.377596459514541</v>
+        <v>0.5996998272732955</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.1016969531774521</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5852000093893223</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.37759628654406</v>
+        <v>0.5996996543028145</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3555172383785248</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.377595989034833</v>
+        <v>0.5996993567935875</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.09053196758031845</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.377595975197194</v>
+        <v>0.5996993429559491</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.377205491065979</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.377595608499775</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.672061562538147</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.377595608499775</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.1622427850961685</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.377595546230402</v>
+        <v>0.5996989139891568</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2383330464363098</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.377595442448113</v>
+        <v>0.5996988102068682</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3563903570175171</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.377595269477632</v>
+        <v>0.5996986372363875</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.1281532347202301</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.377595317909367</v>
+        <v>0.599698685668122</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1953755170106888</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.377594958130767</v>
+        <v>0.599698325889522</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5244887471199036</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.377594916617852</v>
+        <v>0.5996982843766065</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.5574213862419128</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.377594971968406</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3255032896995544</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.37759502731896</v>
+        <v>0.5996983950777143</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.1919505298137665</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5852000093893223</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.377595068831875</v>
+        <v>0.5996984365906296</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2731939256191254</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.377594798997925</v>
+        <v>0.5996981667566795</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.6600940227508545</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1245617031931146</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.377594854348478</v>
+        <v>0.5996982221072334</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3023539185523987</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.377594999643682</v>
+        <v>0.5996983674024374</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.5111985206604004</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.377594965049586</v>
+        <v>0.5996983328083412</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2988669276237488</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.377594951211948</v>
+        <v>0.5996983189707026</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.9188511371612549</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.377595041156598</v>
+        <v>0.5996984089153528</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.7975968718528748</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.377595359422282</v>
+        <v>0.5996987271810374</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1195942685008049</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.377595179532982</v>
+        <v>0.5996985472917373</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.1790875494480133</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.377595221045898</v>
+        <v>0.5996985888046527</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4941155016422272</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.377595034237779</v>
+        <v>0.5996984019965333</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.1542213261127472</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.377595103425971</v>
+        <v>0.5996984711847259</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3810056746006012</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.377594902780213</v>
+        <v>0.5996982705389681</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4498691260814667</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1245617031931146</v>
+        <v>0.72</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.377594944293129</v>
+        <v>0.5996983120518834</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.6237831115722656</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2057574499049892</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.377594971968406</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_5_000006.xlsx
+++ b/out/MLP-mamba2_repeat_5_000006.xlsx
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.6547783017158508</v>
+        <v>0.6547783613204956</v>
       </c>
       <c r="JB5" t="n">
         <v>0.5799999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.6162081360816956</v>
+        <v>0.6162081956863403</v>
       </c>
       <c r="JB7" t="n">
         <v>0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.32485231757164</v>
+        <v>0.3248523473739624</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.4399999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.651511013507843</v>
+        <v>0.6515108942985535</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.5799999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.3148402869701385</v>
+        <v>0.3148402273654938</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.5331536531448364</v>
+        <v>0.5331537127494812</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.385403573513031</v>
+        <v>0.3854036033153534</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3247998654842377</v>
+        <v>0.3247998356819153</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.6990628838539124</v>
+        <v>0.6990629434585571</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.2815493941307068</v>
+        <v>0.2815494537353516</v>
       </c>
       <c r="JB26" t="n">
         <v>0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.5664863586425781</v>
+        <v>0.5664862990379333</v>
       </c>
       <c r="JB28" t="n">
         <v>0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3253392279148102</v>
+        <v>0.3253391981124878</v>
       </c>
       <c r="JB30" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3015113472938538</v>
+        <v>0.3015113174915314</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4891141057014465</v>
+        <v>0.4891140460968018</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.4116252958774567</v>
+        <v>0.4116253256797791</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.669799268245697</v>
+        <v>0.6697992086410522</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.351017951965332</v>
+        <v>0.3510179817676544</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.03590704873204231</v>
+        <v>0.03590704128146172</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.7025089859962463</v>
+        <v>0.7025089263916016</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.8623257875442505</v>
+        <v>0.8623257279396057</v>
       </c>
       <c r="JB54" t="n">
         <v>0.4399999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.5764890313148499</v>
+        <v>0.5764890909194946</v>
       </c>
       <c r="JB56" t="n">
         <v>0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.68604576587677</v>
+        <v>0.6860457062721252</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.537279486656189</v>
+        <v>0.5372794270515442</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.1600000000000001</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.9104500412940979</v>
+        <v>0.9104501605033875</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.6095370054244995</v>
+        <v>0.6095372438430786</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.1962161064147949</v>
+        <v>0.1962161511182785</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.1132867559790611</v>
+        <v>0.1132867857813835</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.1033474057912827</v>
+        <v>0.1033474430441856</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1689743995666504</v>
+        <v>0.1689744740724564</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.7095217108726501</v>
+        <v>0.7095215916633606</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.2720710337162018</v>
+        <v>0.2720710635185242</v>
       </c>
       <c r="JB68" t="n">
         <v>0.02000000000000007</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.4985755383968353</v>
+        <v>0.4985754787921906</v>
       </c>
       <c r="JB69" t="n">
         <v>0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1241387575864792</v>
+        <v>0.1241386979818344</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.2599999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.05662895739078522</v>
+        <v>0.05662901327013969</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.8599999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.09818444401025772</v>
+        <v>0.09818446636199951</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.2276037633419037</v>
+        <v>0.2276038080453873</v>
       </c>
       <c r="JB79" t="n">
         <v>0.16</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.2689307630062103</v>
+        <v>0.2689307332038879</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.779538631439209</v>
+        <v>0.7795385122299194</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5412673950195312</v>
+        <v>0.5412673354148865</v>
       </c>
       <c r="JB83" t="n">
         <v>0.4399999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.6429377198219299</v>
+        <v>0.6429376602172852</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.2159094661474228</v>
+        <v>0.2159094214439392</v>
       </c>
       <c r="JB86" t="n">
         <v>0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.6667807102203369</v>
+        <v>0.6667806506156921</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.5799999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.2760295569896698</v>
+        <v>0.2760296165943146</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.1600000000000001</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.3919332325458527</v>
+        <v>0.391933262348175</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.2424729317426682</v>
+        <v>0.2424729019403458</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.1754699051380157</v>
+        <v>0.1754699200391769</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.2487944066524506</v>
+        <v>0.2487943768501282</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.6692742109298706</v>
+        <v>0.6692740917205811</v>
       </c>
       <c r="JB96" t="n">
         <v>0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3608028292655945</v>
+        <v>0.3608026504516602</v>
       </c>
       <c r="JB98" t="n">
         <v>0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.3555172383785248</v>
+        <v>0.3555172085762024</v>
       </c>
       <c r="JB100" t="n">
         <v>0.1600000000000001</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.1622427850961685</v>
+        <v>0.1622428447008133</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.3563903570175171</v>
+        <v>0.3563903272151947</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.1281532347202301</v>
+        <v>0.1281531900167465</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.1953755170106888</v>
+        <v>0.1953755021095276</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.5244887471199036</v>
+        <v>0.5244888067245483</v>
       </c>
       <c r="JB109" t="n">
         <v>0.1600000000000001</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.5574213862419128</v>
+        <v>0.5574213266372681</v>
       </c>
       <c r="JB110" t="n">
         <v>0.1600000000000001</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.9188511371612549</v>
+        <v>0.9188510179519653</v>
       </c>
       <c r="JB118" t="n">
         <v>0.4399999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.7975968718528748</v>
+        <v>0.79759681224823</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1600000000000001</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.1790875494480133</v>
+        <v>0.1790875941514969</v>
       </c>
       <c r="JB121" t="n">
         <v>0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.4941155016422272</v>
+        <v>0.4941154718399048</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.1542213261127472</v>
+        <v>0.1542212963104248</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.3810056746006012</v>
+        <v>0.3810057044029236</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
